--- a/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/si_contracts.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/si_contracts.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -506,21 +506,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.9</v>
+        <v>21</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2028-11-19</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Outcome</t>
         </is>
       </c>
     </row>
@@ -532,30 +532,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.7</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2027-04-06</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>T&amp;M</t>
         </is>
       </c>
     </row>
@@ -572,25 +572,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.4</v>
+        <v>18.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2028-06-07</t>
+          <t>2027-03-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>T&amp;M</t>
+          <t>Outcome</t>
         </is>
       </c>
     </row>
@@ -602,30 +602,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.2</v>
+        <v>2.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2027-04-16</t>
+          <t>2028-12-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -646,21 +646,21 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.2</v>
+        <v>5.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2027-06-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>T&amp;M</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -681,21 +681,21 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22.8</v>
+        <v>12.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2027-05-19</t>
+          <t>2027-06-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -712,20 +712,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.5</v>
+        <v>36.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2028-04-23</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -742,25 +742,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.6</v>
+        <v>4.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2027-03-16</t>
+          <t>2028-01-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -777,30 +777,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>29.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2027-06-09</t>
+          <t>2028-01-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Outcome</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -821,16 +821,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>38.2</v>
+        <v>30</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-07-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -847,30 +847,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2027-08-24</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>T&amp;M</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -882,25 +882,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.5</v>
+        <v>28.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -917,30 +917,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>S/4HANA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19.6</v>
+        <v>3.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2027-08-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>T&amp;M</t>
+          <t>Outcome</t>
         </is>
       </c>
     </row>
@@ -952,30 +952,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26.9</v>
+        <v>26</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>T&amp;M</t>
         </is>
       </c>
     </row>
@@ -987,30 +987,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.9</v>
+        <v>24.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2027-04-11</t>
+          <t>2028-06-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Outcome</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23.2</v>
+        <v>10.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2028-12-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>T&amp;M</t>
         </is>
       </c>
     </row>
@@ -1062,25 +1062,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.1</v>
+        <v>34.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2027-05-07</t>
+          <t>2027-08-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>T&amp;M</t>
         </is>
       </c>
     </row>
@@ -1092,30 +1092,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.9</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2027-03-11</t>
+          <t>2027-08-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>T&amp;M</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1136,21 +1136,21 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25</v>
+        <v>35.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2028-01-17</t>
+          <t>2027-08-31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>T&amp;M</t>
         </is>
       </c>
     </row>
@@ -1162,30 +1162,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S/4HANA</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.9</v>
+        <v>11.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2027-09-05</t>
+          <t>2027-07-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>T&amp;M</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
